--- a/policy_20260904.xlsx
+++ b/policy_20260904.xlsx
@@ -2510,28 +2510,28 @@
         <v>0</v>
       </c>
       <c r="J23" s="2">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="P23" s="2">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="2">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="S23" s="1"/>
     </row>

--- a/policy_20260904.xlsx
+++ b/policy_20260904.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -2219,7 +2219,7 @@
         <v>350000</v>
       </c>
       <c r="C18" s="4">
-        <v>330000</v>
+        <v>350000</v>
       </c>
       <c r="D18" s="4">
         <v>400000</v>
@@ -2381,13 +2381,13 @@
         <v>350000</v>
       </c>
       <c r="C21" s="4">
-        <v>290000</v>
+        <v>350000</v>
       </c>
       <c r="D21" s="4">
         <v>400000</v>
       </c>
       <c r="E21" s="4">
-        <v>340000</v>
+        <v>380000</v>
       </c>
       <c r="F21" s="2">
         <v>400000</v>

--- a/policy_20260904.xlsx
+++ b/policy_20260904.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A9002B-F6FF-448A-819F-CA48DAC59548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6375" yWindow="4290" windowWidth="26505" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6375" yWindow="4290" windowWidth="26505" windowHeight="14550" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="추가지원금" sheetId="1" r:id="rId1"/>
@@ -8641,82 +8641,82 @@
         <v>36</v>
       </c>
       <c r="B22" s="3">
-        <v>55000</v>
+        <v>115000</v>
       </c>
       <c r="C22" s="3">
-        <v>82000</v>
+        <v>133000</v>
       </c>
       <c r="D22" s="3">
-        <v>109000</v>
+        <v>151000</v>
       </c>
       <c r="E22" s="3">
-        <v>156000</v>
+        <v>183000</v>
       </c>
       <c r="F22" s="3">
-        <v>196000</v>
+        <v>210000</v>
       </c>
       <c r="G22" s="3">
-        <v>223000</v>
+        <v>228000</v>
       </c>
       <c r="H22" s="3">
-        <v>230000</v>
+        <v>233000</v>
       </c>
       <c r="I22" s="3">
-        <v>236000</v>
+        <v>237000</v>
       </c>
       <c r="J22" s="3">
-        <v>263000</v>
+        <v>255000</v>
       </c>
       <c r="K22" s="3">
-        <v>270000</v>
+        <v>260000</v>
       </c>
       <c r="L22" s="3">
-        <v>283000</v>
+        <v>269000</v>
       </c>
       <c r="M22" s="3">
-        <v>290000</v>
+        <v>273000</v>
       </c>
       <c r="N22" s="3">
-        <v>330000</v>
+        <v>300000</v>
       </c>
       <c r="O22" s="3">
-        <v>357000</v>
+        <v>319000</v>
       </c>
       <c r="P22" s="3">
+        <v>332000</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>346000</v>
+      </c>
+      <c r="R22" s="3">
+        <v>355000</v>
+      </c>
+      <c r="S22" s="3">
+        <v>364000</v>
+      </c>
+      <c r="T22" s="3">
         <v>377000</v>
       </c>
-      <c r="Q22" s="3">
-        <v>398000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>411000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>425000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>445000</v>
-      </c>
       <c r="U22" s="3">
-        <v>498000</v>
+        <v>413000</v>
       </c>
       <c r="V22" s="3">
-        <v>530000</v>
+        <v>450000</v>
       </c>
       <c r="W22" s="3">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="X22" s="3">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="Y22" s="3">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="Z22" s="3">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="AA22" s="3">
-        <v>600000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
